--- a/rag/excel/performance.xlsx
+++ b/rag/excel/performance.xlsx
@@ -505,17 +505,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.01</v>
+        <v>0.66</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01</v>
+        <v>0.6</v>
       </c>
       <c r="E3" t="n">
-        <v>1.13456</v>
+        <v>-4.02952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1m14s</t>
+          <t>34m14s</t>
         </is>
       </c>
     </row>
@@ -554,10 +554,20 @@
           <t>Rag</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.18849</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>70m49s</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -594,10 +604,20 @@
           <t>Rag</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-9.938840000000001</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>312m21s</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>

--- a/rag/excel/performance.xlsx
+++ b/rag/excel/performance.xlsx
@@ -505,17 +505,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.02952</v>
+        <v>261511784300.2776</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>34m14s</t>
+          <t>0m41s</t>
         </is>
       </c>
     </row>

--- a/rag/excel/performance.xlsx
+++ b/rag/excel/performance.xlsx
@@ -505,17 +505,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="E3" t="n">
-        <v>261511784300.2776</v>
+        <v>121026780317.4731</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0m41s</t>
+          <t>34m14s</t>
         </is>
       </c>
     </row>

--- a/rag/excel/performance.xlsx
+++ b/rag/excel/performance.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,6 +688,32 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>3m36s</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Rag</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>phi4_rag</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>11m8s</t>
         </is>
       </c>
     </row>

--- a/rag/excel/performance.xlsx
+++ b/rag/excel/performance.xlsx
@@ -703,17 +703,17 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11m8s</t>
+          <t>7m41s</t>
         </is>
       </c>
     </row>
